--- a/artfynd/A 34094-2025 artfynd.xlsx
+++ b/artfynd/A 34094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439175</v>
       </c>
       <c r="B2" t="n">
-        <v>99380</v>
+        <v>99383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2025 artfynd.xlsx
+++ b/artfynd/A 34094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439175</v>
       </c>
       <c r="B2" t="n">
-        <v>99383</v>
+        <v>99384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2025 artfynd.xlsx
+++ b/artfynd/A 34094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439175</v>
       </c>
       <c r="B2" t="n">
-        <v>99384</v>
+        <v>99389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2025 artfynd.xlsx
+++ b/artfynd/A 34094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439175</v>
       </c>
       <c r="B2" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2025 artfynd.xlsx
+++ b/artfynd/A 34094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439175</v>
       </c>
       <c r="B2" t="n">
-        <v>99391</v>
+        <v>99397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2025 artfynd.xlsx
+++ b/artfynd/A 34094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439175</v>
       </c>
       <c r="B2" t="n">
-        <v>99397</v>
+        <v>99399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2025 artfynd.xlsx
+++ b/artfynd/A 34094-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439175</v>
       </c>
       <c r="B2" t="n">
-        <v>99399</v>
+        <v>99400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
